--- a/Tijd.xlsx
+++ b/Tijd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\New Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucp13626\Documents\Repositories\2026_Janssen_CellProportionEstimation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EE4DF2-535D-4498-8BCB-79DD9744162F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8060222-0D12-4115-95B6-73AF9E8BCE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -364,13 +361,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -381,10 +378,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
       <c r="C2">
         <f>SUM(B:B)</f>
-        <v>0</v>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B3">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/Tijd.xlsx
+++ b/Tijd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucp13626\Documents\Repositories\2026_Janssen_CellProportionEstimation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8060222-0D12-4115-95B6-73AF9E8BCE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E81EC30-8775-4ED7-AE6D-B78A2C3D88ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -361,7 +361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -387,7 +387,7 @@
       </c>
       <c r="C2">
         <f>SUM(B:B)</f>
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -396,6 +396,22 @@
       </c>
       <c r="B3">
         <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
